--- a/results/04_bray_curtis_NMDS/tables/zci_summary.xlsx
+++ b/results/04_bray_curtis_NMDS/tables/zci_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,32 +503,32 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3850206317554953</v>
+        <v>0.4004822262034736</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6709293694492442</v>
+        <v>0.5753977136694821</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5021568172127482</v>
+        <v>0.4946243288061744</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07020510111189798</v>
+        <v>0.02931726783750499</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.232589686615795</v>
+        <v>-0.2820391855075032</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00358745478019741</v>
+        <v>4.37269635730107e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2101060230092488</v>
+        <v>-0.2758110603741993</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008690850238764756</v>
+        <v>6.527316153595632e-05</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
     </row>
@@ -573,44 +573,6 @@
           <t>**</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Centroid-Proj</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-4.483842250602508</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10.33384404882573</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.629541467362518</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.473790964464976</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.08364049082039096</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5677476961410521</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.1269420138681905</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.3847494589608303</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/04_bray_curtis_NMDS/tables/zci_summary.xlsx
+++ b/results/04_bray_curtis_NMDS/tables/zci_summary.xlsx
@@ -503,32 +503,32 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4004822262034736</v>
+        <v>0.2717873776870258</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5753977136694821</v>
+        <v>0.6701076455213898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4946243288061744</v>
+        <v>0.4675989033263008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02931726783750499</v>
+        <v>0.09106463904171641</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2820391855075032</v>
+        <v>-0.1770356729172198</v>
       </c>
       <c r="I2" t="n">
-        <v>4.37269635730107e-05</v>
+        <v>0.012821439425342</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2758110603741993</v>
+        <v>-0.1525170393216674</v>
       </c>
       <c r="K2" t="n">
-        <v>6.527316153595632e-05</v>
+        <v>0.03238798430772881</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>***</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -545,28 +545,28 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03765064129899173</v>
+        <v>0.1001575263097882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7968891574504354</v>
+        <v>0.9296927209247681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4257578548242389</v>
+        <v>0.6459984079502699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2398463694261486</v>
+        <v>0.261853611546186</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4863562277239132</v>
+        <v>-0.4834804354326673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007468906119985669</v>
+        <v>0.002815467339123949</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4249291816934121</v>
+        <v>-0.4308880308880309</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02157425306551554</v>
+        <v>0.008702685937341059</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
